--- a/finance/_refresh_indrive.xlsx
+++ b/finance/_refresh_indrive.xlsx
@@ -53,8 +53,8 @@
     <definedName name="load_sel">'Assumptions'!$B$49</definedName>
     <definedName name="revleg_sel">'Assumptions'!$B$50</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$5</definedName>
-    <definedName name="som_floor_fleet">'Corridor economics'!$D$16</definedName>
-    <definedName name="som_floor_rev">'Corridor economics'!$E$16</definedName>
+    <definedName name="som_floor_fleet">'Corridor economics'!$D$19</definedName>
+    <definedName name="som_floor_rev">'Corridor economics'!$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2348,7 +2348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA16"/>
+  <dimension ref="A1:BA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3123,25 +3123,17 @@
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>Praça XV Terminal (central Rio) → Cocotá Terminal (Ilha do Governador)</t>
+          <t>Beira Mar Terminal (continent) → Miramar Terminal (Florianopolis island)</t>
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>6</v>
+        <v>4.79</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>28</v>
-      </c>
-      <c r="F6" s="34" t="inlineStr">
-        <is>
-          <t>T1/T2</t>
-        </is>
-      </c>
-      <c r="G6" s="34" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F6" s="34" t="n"/>
+      <c r="G6" s="34" t="n"/>
       <c r="H6" s="20" t="n">
         <v>1</v>
       </c>
@@ -3246,16 +3238,16 @@
         <v/>
       </c>
       <c r="AH6" s="33" t="n">
-        <v>278607</v>
+        <v>6100556</v>
       </c>
       <c r="AI6" s="34" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AJ6" s="34" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med-low</t>
         </is>
       </c>
       <c r="AK6" s="41" t="n">
@@ -3302,19 +3294,15 @@
         <f>IF(((T6*pax_cap*load_full*IF(ABS(MOD(ABS((L6*M6*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L6*M6*revleg_full)/2,0),ROUND((L6*M6*revleg_full),0)))-(((battery/range_nm)*D6*IF(ABS(MOD(ABS((L6*M6*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L6*M6*revleg_full)/2,0),ROUND((L6*M6*revleg_full),0))*VLOOKUP(B6,country_opex,3,FALSE))+W6+X6+Y6+Z6+AA6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((T6*pax_cap*load_full*IF(ABS(MOD(ABS((L6*M6*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L6*M6*revleg_full)/2,0),ROUND((L6*M6*revleg_full),0)))-(((battery/range_nm)*D6*IF(ABS(MOD(ABS((L6*M6*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L6*M6*revleg_full)/2,0),ROUND((L6*M6*revleg_full),0))*VLOOKUP(B6,country_opex,3,FALSE))+W6+X6+Y6+Z6+AA6)))</f>
         <v/>
       </c>
-      <c r="AY6" s="46" t="inlineStr">
-        <is>
-          <t>https://barcasrio.com.br/linhas-horarios-e-tarifas/</t>
-        </is>
-      </c>
+      <c r="AY6" s="46" t="n"/>
       <c r="AZ6" s="46" t="inlineStr">
         <is>
-          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+          <t>https://www.sie.sc.gov.br/webdocs/sie/doc-tecnicos/aquaviario/ (EVTE Aquaviario RMF, Relatorio 3 - Componente Demanda; SIE-SC + BID)</t>
         </is>
       </c>
       <c r="BA6" s="34" t="inlineStr">
         <is>
-          <t>rn-369ef0eb69d9</t>
+          <t>rn-floripa-r4-PROV</t>
         </is>
       </c>
     </row>
@@ -3331,25 +3319,17 @@
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>Praça XV Terminal (central Rio) → Paquetá Island Terminal</t>
+          <t>Barreiros Terminal (Sao Jose / continent) → Miramar Terminal (Florianopolis island)</t>
         </is>
       </c>
       <c r="D7" s="33" t="n">
-        <v>9.199999999999999</v>
+        <v>4.99</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>28</v>
-      </c>
-      <c r="F7" s="34" t="inlineStr">
-        <is>
-          <t>T1/T2</t>
-        </is>
-      </c>
-      <c r="G7" s="34" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
       <c r="H7" s="20" t="n">
         <v>1</v>
       </c>
@@ -3454,16 +3434,16 @@
         <v/>
       </c>
       <c r="AH7" s="33" t="n">
-        <v>1170652</v>
+        <v>3890964</v>
       </c>
       <c r="AI7" s="34" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AJ7" s="34" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med-low</t>
         </is>
       </c>
       <c r="AK7" s="41" t="n">
@@ -3510,46 +3490,50 @@
         <f>IF(((T7*pax_cap*load_full*IF(ABS(MOD(ABS((L7*M7*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L7*M7*revleg_full)/2,0),ROUND((L7*M7*revleg_full),0)))-(((battery/range_nm)*D7*IF(ABS(MOD(ABS((L7*M7*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L7*M7*revleg_full)/2,0),ROUND((L7*M7*revleg_full),0))*VLOOKUP(B7,country_opex,3,FALSE))+W7+X7+Y7+Z7+AA7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((T7*pax_cap*load_full*IF(ABS(MOD(ABS((L7*M7*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L7*M7*revleg_full)/2,0),ROUND((L7*M7*revleg_full),0)))-(((battery/range_nm)*D7*IF(ABS(MOD(ABS((L7*M7*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L7*M7*revleg_full)/2,0),ROUND((L7*M7*revleg_full),0))*VLOOKUP(B7,country_opex,3,FALSE))+W7+X7+Y7+Z7+AA7)))</f>
         <v/>
       </c>
-      <c r="AY7" s="46" t="inlineStr">
-        <is>
-          <t>https://barcasrio.com.br/linhas-horarios-e-tarifas/</t>
-        </is>
-      </c>
+      <c r="AY7" s="46" t="n"/>
       <c r="AZ7" s="46" t="inlineStr">
         <is>
-          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+          <t>https://www.sie.sc.gov.br/webdocs/sie/doc-tecnicos/aquaviario/ (EVTE Aquaviario RMF, Relatorio 3 - Componente Demanda; SIE-SC + BID)</t>
         </is>
       </c>
       <c r="BA7" s="34" t="inlineStr">
         <is>
-          <t>rn-00bb6ded4be5</t>
+          <t>rn-floripa-r3-PROV</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
         <is>
-          <t>Indrive Egypt</t>
+          <t>Indrive Brazil</t>
         </is>
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>Hurghada Marina → Giftun Island (Orange Bay / Mahmya)</t>
+          <t>Praça XV Terminal (central Rio) → Cocotá Terminal (Ilha do Governador)</t>
         </is>
       </c>
       <c r="D8" s="33" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>32</v>
-      </c>
-      <c r="F8" s="34" t="n"/>
-      <c r="G8" s="34" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="F8" s="34" t="inlineStr">
+        <is>
+          <t>T1/T2</t>
+        </is>
+      </c>
+      <c r="G8" s="34" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
       <c r="H8" s="20" t="n">
         <v>1</v>
       </c>
@@ -3654,12 +3638,20 @@
         <v/>
       </c>
       <c r="AH8" s="33" t="n">
-        <v>187512</v>
-      </c>
-      <c r="AI8" s="34" t="n"/>
-      <c r="AJ8" s="34" t="n"/>
+        <v>278607</v>
+      </c>
+      <c r="AI8" s="34" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AJ8" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AK8" s="41" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="AL8" s="36">
         <f>IF(AH8="","",AH8*AK8)</f>
@@ -3702,38 +3694,54 @@
         <f>IF(((T8*pax_cap*load_full*IF(ABS(MOD(ABS((L8*M8*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L8*M8*revleg_full)/2,0),ROUND((L8*M8*revleg_full),0)))-(((battery/range_nm)*D8*IF(ABS(MOD(ABS((L8*M8*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L8*M8*revleg_full)/2,0),ROUND((L8*M8*revleg_full),0))*VLOOKUP(B8,country_opex,3,FALSE))+W8+X8+Y8+Z8+AA8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((T8*pax_cap*load_full*IF(ABS(MOD(ABS((L8*M8*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L8*M8*revleg_full)/2,0),ROUND((L8*M8*revleg_full),0)))-(((battery/range_nm)*D8*IF(ABS(MOD(ABS((L8*M8*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L8*M8*revleg_full)/2,0),ROUND((L8*M8*revleg_full),0))*VLOOKUP(B8,country_opex,3,FALSE))+W8+X8+Y8+Z8+AA8)))</f>
         <v/>
       </c>
-      <c r="AY8" s="46" t="n"/>
-      <c r="AZ8" s="46" t="n"/>
+      <c r="AY8" s="46" t="inlineStr">
+        <is>
+          <t>https://barcasrio.com.br/linhas-horarios-e-tarifas/</t>
+        </is>
+      </c>
+      <c r="AZ8" s="46" t="inlineStr">
+        <is>
+          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+        </is>
+      </c>
       <c r="BA8" s="34" t="inlineStr">
         <is>
-          <t>rn-b06f6971ed47</t>
+          <t>rn-369ef0eb69d9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>Indrive Egypt</t>
+          <t>Indrive Brazil</t>
         </is>
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>Sharm Marina (Sharm El Maya / Old Market Harbour) → Ras Mohammed (reef jetty)</t>
+          <t>Praça XV Terminal (central Rio) → Paquetá Island Terminal</t>
         </is>
       </c>
       <c r="D9" s="33" t="n">
-        <v>11.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E9" s="27" t="n">
-        <v>50</v>
-      </c>
-      <c r="F9" s="34" t="n"/>
-      <c r="G9" s="34" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>T1/T2</t>
+        </is>
+      </c>
+      <c r="G9" s="34" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
       <c r="H9" s="20" t="n">
         <v>1</v>
       </c>
@@ -3838,12 +3846,20 @@
         <v/>
       </c>
       <c r="AH9" s="33" t="n">
-        <v>50000</v>
-      </c>
-      <c r="AI9" s="34" t="n"/>
-      <c r="AJ9" s="34" t="n"/>
+        <v>1170652</v>
+      </c>
+      <c r="AI9" s="34" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AJ9" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AK9" s="41" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="AL9" s="36">
         <f>IF(AH9="","",AH9*AK9)</f>
@@ -3886,144 +3902,728 @@
         <f>IF(((T9*pax_cap*load_full*IF(ABS(MOD(ABS((L9*M9*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L9*M9*revleg_full)/2,0),ROUND((L9*M9*revleg_full),0)))-(((battery/range_nm)*D9*IF(ABS(MOD(ABS((L9*M9*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L9*M9*revleg_full)/2,0),ROUND((L9*M9*revleg_full),0))*VLOOKUP(B9,country_opex,3,FALSE))+W9+X9+Y9+Z9+AA9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((T9*pax_cap*load_full*IF(ABS(MOD(ABS((L9*M9*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L9*M9*revleg_full)/2,0),ROUND((L9*M9*revleg_full),0)))-(((battery/range_nm)*D9*IF(ABS(MOD(ABS((L9*M9*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L9*M9*revleg_full)/2,0),ROUND((L9*M9*revleg_full),0))*VLOOKUP(B9,country_opex,3,FALSE))+W9+X9+Y9+Z9+AA9)))</f>
         <v/>
       </c>
-      <c r="AY9" s="46" t="n"/>
-      <c r="AZ9" s="46" t="n"/>
+      <c r="AY9" s="46" t="inlineStr">
+        <is>
+          <t>https://barcasrio.com.br/linhas-horarios-e-tarifas/</t>
+        </is>
+      </c>
+      <c r="AZ9" s="46" t="inlineStr">
+        <is>
+          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+        </is>
+      </c>
       <c r="BA9" s="34" t="inlineStr">
         <is>
+          <t>rn-00bb6ded4be5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>Indrive Brazil</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>Angra dos Reis Terminal (Costa Verde) → Abraão Terminal (Ilha Grande)</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G10" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="35">
+        <f>60*D10/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J10" s="35">
+        <f>IF(B10="South Korea",D10/korea_charge_range_nm*korea_full_range_charge_min,0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="35">
+        <f>IF(B10="South Korea",I10+korea_turn_min+korea_dwell_min+J10,I10+turn_min+dwell_min)</f>
+        <v/>
+      </c>
+      <c r="L10" s="36">
+        <f>IF(B10="South Korea",FLOOR(60*korea_service_hr/K10,1),MIN(15,FLOOR(60*service_hr/K10,1)))</f>
+        <v/>
+      </c>
+      <c r="M10" s="36">
+        <f>IF(ABS(MOD(ABS((365*mech_uptime*H10)),1)-0.5)&lt;1E-9,2*ROUND((365*mech_uptime*H10)/2,0),ROUND((365*mech_uptime*H10),0))</f>
+        <v/>
+      </c>
+      <c r="N10" s="37">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="O10" s="37">
+        <f>IF(AND(B10="South Korea",scenario="MID"),korea_mid_revleg,revleg_sel)</f>
+        <v/>
+      </c>
+      <c r="P10" s="36">
+        <f>IF(ABS(MOD(ABS((L10*M10*O10)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*O10)/2,0),ROUND((L10*M10*O10),0))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="37">
+        <f>IF(AND(B10="South Korea",scenario="MID"),korea_mid_load,load_sel)</f>
+        <v/>
+      </c>
+      <c r="R10" s="38">
+        <f>pax_cap*Q10</f>
+        <v/>
+      </c>
+      <c r="S10" s="36">
+        <f>R10*P10</f>
+        <v/>
+      </c>
+      <c r="T10" s="39">
+        <f>E10*discount</f>
+        <v/>
+      </c>
+      <c r="U10" s="40">
+        <f>T10*S10</f>
+        <v/>
+      </c>
+      <c r="V10" s="40">
+        <f>(battery/range_nm)*D10*P10*VLOOKUP(B10,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="W10" s="40">
+        <f>VLOOKUP(B10,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="X10" s="40">
+        <f>VLOOKUP(B10,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="Y10" s="40">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Z10" s="40">
+        <f>VLOOKUP(B10,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="AA10" s="40">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AB10" s="40">
+        <f>V10+W10+X10+Y10+Z10+AA10</f>
+        <v/>
+      </c>
+      <c r="AC10" s="40">
+        <f>VLOOKUP(B10,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AD10" s="40">
+        <f>U10-AB10</f>
+        <v/>
+      </c>
+      <c r="AE10" s="37">
+        <f>IF(U10=0,"",AD10/U10)</f>
+        <v/>
+      </c>
+      <c r="AF10" s="38">
+        <f>IF(AD10&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/AD10)</f>
+        <v/>
+      </c>
+      <c r="AG10" s="35">
+        <f>((D10*P10/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D10*P10*VLOOKUP(B10,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AH10" s="33" t="n">
+        <v>207993</v>
+      </c>
+      <c r="AI10" s="34" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AJ10" s="34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AK10" s="41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AL10" s="36">
+        <f>IF(AH10="","",AH10*AK10)</f>
+        <v/>
+      </c>
+      <c r="AM10" s="36">
+        <f>IF(OR(AH10="",S10=0),"",MIN(IF(AU10="",9.9E+99,AU10),FLOOR(AL10/S10,1)))</f>
+        <v/>
+      </c>
+      <c r="AN10" s="40">
+        <f>IF(AM10="","",AM10*IF(ABS(MOD(ABS((U10)),1)-0.5)&lt;1E-9,2*ROUND((U10)/2,0),ROUND((U10),0)))</f>
+        <v/>
+      </c>
+      <c r="AO10" s="38">
+        <f>IF(OR(AH10="",S10=0),"",MIN(IF(AU10="",9.9E+99,AU10),AL10/S10))</f>
+        <v/>
+      </c>
+      <c r="AP10" s="40">
+        <f>IF(AO10="","",AO10*IF(B10="South Korea",IF(ABS(MOD(ABS((U10)),1)-0.5)&lt;1E-9,2*ROUND((U10)/2,0),ROUND((U10),0)),U10))</f>
+        <v/>
+      </c>
+      <c r="AQ10" s="42" t="n"/>
+      <c r="AR10" s="34" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AS10" s="43" t="n"/>
+      <c r="AT10" s="43" t="n"/>
+      <c r="AU10" s="44" t="n"/>
+      <c r="AV10" s="45">
+        <f>IF(((T10*pax_cap*load_thin*IF(ABS(MOD(ABS((L10*M10*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_thin)/2,0),ROUND((L10*M10*revleg_thin),0)))-(((battery/range_nm)*D10*IF(ABS(MOD(ABS((L10*M10*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_thin)/2,0),ROUND((L10*M10*revleg_thin),0))*VLOOKUP(B10,country_opex,3,FALSE))+W10+X10+Y10+Z10+AA10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((T10*pax_cap*load_thin*IF(ABS(MOD(ABS((L10*M10*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_thin)/2,0),ROUND((L10*M10*revleg_thin),0)))-(((battery/range_nm)*D10*IF(ABS(MOD(ABS((L10*M10*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_thin)/2,0),ROUND((L10*M10*revleg_thin),0))*VLOOKUP(B10,country_opex,3,FALSE))+W10+X10+Y10+Z10+AA10)))</f>
+        <v/>
+      </c>
+      <c r="AW10" s="45">
+        <f>IF(((T10*pax_cap*IF(B10="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D10*IF(ABS(MOD(ABS((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B10,country_opex,3,FALSE))+W10+X10+Y10+Z10+AA10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((T10*pax_cap*IF(B10="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D10*IF(ABS(MOD(ABS((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L10*M10*IF(B10="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B10,country_opex,3,FALSE))+W10+X10+Y10+Z10+AA10)))</f>
+        <v/>
+      </c>
+      <c r="AX10" s="45">
+        <f>IF(((T10*pax_cap*load_full*IF(ABS(MOD(ABS((L10*M10*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_full)/2,0),ROUND((L10*M10*revleg_full),0)))-(((battery/range_nm)*D10*IF(ABS(MOD(ABS((L10*M10*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_full)/2,0),ROUND((L10*M10*revleg_full),0))*VLOOKUP(B10,country_opex,3,FALSE))+W10+X10+Y10+Z10+AA10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((T10*pax_cap*load_full*IF(ABS(MOD(ABS((L10*M10*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_full)/2,0),ROUND((L10*M10*revleg_full),0)))-(((battery/range_nm)*D10*IF(ABS(MOD(ABS((L10*M10*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L10*M10*revleg_full)/2,0),ROUND((L10*M10*revleg_full),0))*VLOOKUP(B10,country_opex,3,FALSE))+W10+X10+Y10+Z10+AA10)))</f>
+        <v/>
+      </c>
+      <c r="AY10" s="46" t="inlineStr">
+        <is>
+          <t>AGETRANSP / CCR Barcas Costa Verde published tariff</t>
+        </is>
+      </c>
+      <c r="AZ10" s="46" t="inlineStr">
+        <is>
+          <t>https://www2.agetransp.rj.gov.br/arquivos/operacao-servicos/relatorio-de-atividades/Relat%C3%B3rio%20Mensal%20de%20Atividades%20Janeiro%202024.pdf</t>
+        </is>
+      </c>
+      <c r="BA10" s="34" t="inlineStr">
+        <is>
+          <t>rn-angra-abraao-PROV</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>Indrive Egypt</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>Hurghada Marina → Giftun Island (Orange Bay / Mahmya)</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="35">
+        <f>60*D11/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J11" s="35">
+        <f>IF(B11="South Korea",D11/korea_charge_range_nm*korea_full_range_charge_min,0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="35">
+        <f>IF(B11="South Korea",I11+korea_turn_min+korea_dwell_min+J11,I11+turn_min+dwell_min)</f>
+        <v/>
+      </c>
+      <c r="L11" s="36">
+        <f>IF(B11="South Korea",FLOOR(60*korea_service_hr/K11,1),MIN(15,FLOOR(60*service_hr/K11,1)))</f>
+        <v/>
+      </c>
+      <c r="M11" s="36">
+        <f>IF(ABS(MOD(ABS((365*mech_uptime*H11)),1)-0.5)&lt;1E-9,2*ROUND((365*mech_uptime*H11)/2,0),ROUND((365*mech_uptime*H11),0))</f>
+        <v/>
+      </c>
+      <c r="N11" s="37">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="O11" s="37">
+        <f>IF(AND(B11="South Korea",scenario="MID"),korea_mid_revleg,revleg_sel)</f>
+        <v/>
+      </c>
+      <c r="P11" s="36">
+        <f>IF(ABS(MOD(ABS((L11*M11*O11)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*O11)/2,0),ROUND((L11*M11*O11),0))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="37">
+        <f>IF(AND(B11="South Korea",scenario="MID"),korea_mid_load,load_sel)</f>
+        <v/>
+      </c>
+      <c r="R11" s="38">
+        <f>pax_cap*Q11</f>
+        <v/>
+      </c>
+      <c r="S11" s="36">
+        <f>R11*P11</f>
+        <v/>
+      </c>
+      <c r="T11" s="39">
+        <f>E11*discount</f>
+        <v/>
+      </c>
+      <c r="U11" s="40">
+        <f>T11*S11</f>
+        <v/>
+      </c>
+      <c r="V11" s="40">
+        <f>(battery/range_nm)*D11*P11*VLOOKUP(B11,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="W11" s="40">
+        <f>VLOOKUP(B11,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="X11" s="40">
+        <f>VLOOKUP(B11,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="40">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Z11" s="40">
+        <f>VLOOKUP(B11,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="AA11" s="40">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AB11" s="40">
+        <f>V11+W11+X11+Y11+Z11+AA11</f>
+        <v/>
+      </c>
+      <c r="AC11" s="40">
+        <f>VLOOKUP(B11,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AD11" s="40">
+        <f>U11-AB11</f>
+        <v/>
+      </c>
+      <c r="AE11" s="37">
+        <f>IF(U11=0,"",AD11/U11)</f>
+        <v/>
+      </c>
+      <c r="AF11" s="38">
+        <f>IF(AD11&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/AD11)</f>
+        <v/>
+      </c>
+      <c r="AG11" s="35">
+        <f>((D11*P11/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D11*P11*VLOOKUP(B11,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AH11" s="33" t="n">
+        <v>187512</v>
+      </c>
+      <c r="AI11" s="34" t="n"/>
+      <c r="AJ11" s="34" t="n"/>
+      <c r="AK11" s="41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AL11" s="36">
+        <f>IF(AH11="","",AH11*AK11)</f>
+        <v/>
+      </c>
+      <c r="AM11" s="36">
+        <f>IF(OR(AH11="",S11=0),"",MIN(IF(AU11="",9.9E+99,AU11),FLOOR(AL11/S11,1)))</f>
+        <v/>
+      </c>
+      <c r="AN11" s="40">
+        <f>IF(AM11="","",AM11*IF(ABS(MOD(ABS((U11)),1)-0.5)&lt;1E-9,2*ROUND((U11)/2,0),ROUND((U11),0)))</f>
+        <v/>
+      </c>
+      <c r="AO11" s="38">
+        <f>IF(OR(AH11="",S11=0),"",MIN(IF(AU11="",9.9E+99,AU11),AL11/S11))</f>
+        <v/>
+      </c>
+      <c r="AP11" s="40">
+        <f>IF(AO11="","",AO11*IF(B11="South Korea",IF(ABS(MOD(ABS((U11)),1)-0.5)&lt;1E-9,2*ROUND((U11)/2,0),ROUND((U11),0)),U11))</f>
+        <v/>
+      </c>
+      <c r="AQ11" s="42" t="n"/>
+      <c r="AR11" s="34" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AS11" s="43" t="n"/>
+      <c r="AT11" s="43" t="n"/>
+      <c r="AU11" s="44" t="n"/>
+      <c r="AV11" s="45">
+        <f>IF(((T11*pax_cap*load_thin*IF(ABS(MOD(ABS((L11*M11*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_thin)/2,0),ROUND((L11*M11*revleg_thin),0)))-(((battery/range_nm)*D11*IF(ABS(MOD(ABS((L11*M11*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_thin)/2,0),ROUND((L11*M11*revleg_thin),0))*VLOOKUP(B11,country_opex,3,FALSE))+W11+X11+Y11+Z11+AA11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((T11*pax_cap*load_thin*IF(ABS(MOD(ABS((L11*M11*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_thin)/2,0),ROUND((L11*M11*revleg_thin),0)))-(((battery/range_nm)*D11*IF(ABS(MOD(ABS((L11*M11*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_thin)/2,0),ROUND((L11*M11*revleg_thin),0))*VLOOKUP(B11,country_opex,3,FALSE))+W11+X11+Y11+Z11+AA11)))</f>
+        <v/>
+      </c>
+      <c r="AW11" s="45">
+        <f>IF(((T11*pax_cap*IF(B11="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D11*IF(ABS(MOD(ABS((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B11,country_opex,3,FALSE))+W11+X11+Y11+Z11+AA11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((T11*pax_cap*IF(B11="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D11*IF(ABS(MOD(ABS((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L11*M11*IF(B11="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B11,country_opex,3,FALSE))+W11+X11+Y11+Z11+AA11)))</f>
+        <v/>
+      </c>
+      <c r="AX11" s="45">
+        <f>IF(((T11*pax_cap*load_full*IF(ABS(MOD(ABS((L11*M11*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_full)/2,0),ROUND((L11*M11*revleg_full),0)))-(((battery/range_nm)*D11*IF(ABS(MOD(ABS((L11*M11*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_full)/2,0),ROUND((L11*M11*revleg_full),0))*VLOOKUP(B11,country_opex,3,FALSE))+W11+X11+Y11+Z11+AA11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((T11*pax_cap*load_full*IF(ABS(MOD(ABS((L11*M11*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_full)/2,0),ROUND((L11*M11*revleg_full),0)))-(((battery/range_nm)*D11*IF(ABS(MOD(ABS((L11*M11*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L11*M11*revleg_full)/2,0),ROUND((L11*M11*revleg_full),0))*VLOOKUP(B11,country_opex,3,FALSE))+W11+X11+Y11+Z11+AA11)))</f>
+        <v/>
+      </c>
+      <c r="AY11" s="46" t="n"/>
+      <c r="AZ11" s="46" t="n"/>
+      <c r="BA11" s="34" t="inlineStr">
+        <is>
+          <t>rn-b06f6971ed47</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Indrive Egypt</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>Sharm Marina (Sharm El Maya / Old Market Harbour) → Ras Mohammed (reef jetty)</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E12" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" s="34" t="n"/>
+      <c r="G12" s="34" t="n"/>
+      <c r="H12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="35">
+        <f>60*D12/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J12" s="35">
+        <f>IF(B12="South Korea",D12/korea_charge_range_nm*korea_full_range_charge_min,0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="35">
+        <f>IF(B12="South Korea",I12+korea_turn_min+korea_dwell_min+J12,I12+turn_min+dwell_min)</f>
+        <v/>
+      </c>
+      <c r="L12" s="36">
+        <f>IF(B12="South Korea",FLOOR(60*korea_service_hr/K12,1),MIN(15,FLOOR(60*service_hr/K12,1)))</f>
+        <v/>
+      </c>
+      <c r="M12" s="36">
+        <f>IF(ABS(MOD(ABS((365*mech_uptime*H12)),1)-0.5)&lt;1E-9,2*ROUND((365*mech_uptime*H12)/2,0),ROUND((365*mech_uptime*H12),0))</f>
+        <v/>
+      </c>
+      <c r="N12" s="37">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="O12" s="37">
+        <f>IF(AND(B12="South Korea",scenario="MID"),korea_mid_revleg,revleg_sel)</f>
+        <v/>
+      </c>
+      <c r="P12" s="36">
+        <f>IF(ABS(MOD(ABS((L12*M12*O12)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*O12)/2,0),ROUND((L12*M12*O12),0))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="37">
+        <f>IF(AND(B12="South Korea",scenario="MID"),korea_mid_load,load_sel)</f>
+        <v/>
+      </c>
+      <c r="R12" s="38">
+        <f>pax_cap*Q12</f>
+        <v/>
+      </c>
+      <c r="S12" s="36">
+        <f>R12*P12</f>
+        <v/>
+      </c>
+      <c r="T12" s="39">
+        <f>E12*discount</f>
+        <v/>
+      </c>
+      <c r="U12" s="40">
+        <f>T12*S12</f>
+        <v/>
+      </c>
+      <c r="V12" s="40">
+        <f>(battery/range_nm)*D12*P12*VLOOKUP(B12,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="W12" s="40">
+        <f>VLOOKUP(B12,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="X12" s="40">
+        <f>VLOOKUP(B12,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="Y12" s="40">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Z12" s="40">
+        <f>VLOOKUP(B12,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="AA12" s="40">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AB12" s="40">
+        <f>V12+W12+X12+Y12+Z12+AA12</f>
+        <v/>
+      </c>
+      <c r="AC12" s="40">
+        <f>VLOOKUP(B12,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AD12" s="40">
+        <f>U12-AB12</f>
+        <v/>
+      </c>
+      <c r="AE12" s="37">
+        <f>IF(U12=0,"",AD12/U12)</f>
+        <v/>
+      </c>
+      <c r="AF12" s="38">
+        <f>IF(AD12&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/AD12)</f>
+        <v/>
+      </c>
+      <c r="AG12" s="35">
+        <f>((D12*P12/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D12*P12*VLOOKUP(B12,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AH12" s="33" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AI12" s="34" t="n"/>
+      <c r="AJ12" s="34" t="n"/>
+      <c r="AK12" s="41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AL12" s="36">
+        <f>IF(AH12="","",AH12*AK12)</f>
+        <v/>
+      </c>
+      <c r="AM12" s="36">
+        <f>IF(OR(AH12="",S12=0),"",MIN(IF(AU12="",9.9E+99,AU12),FLOOR(AL12/S12,1)))</f>
+        <v/>
+      </c>
+      <c r="AN12" s="40">
+        <f>IF(AM12="","",AM12*IF(ABS(MOD(ABS((U12)),1)-0.5)&lt;1E-9,2*ROUND((U12)/2,0),ROUND((U12),0)))</f>
+        <v/>
+      </c>
+      <c r="AO12" s="38">
+        <f>IF(OR(AH12="",S12=0),"",MIN(IF(AU12="",9.9E+99,AU12),AL12/S12))</f>
+        <v/>
+      </c>
+      <c r="AP12" s="40">
+        <f>IF(AO12="","",AO12*IF(B12="South Korea",IF(ABS(MOD(ABS((U12)),1)-0.5)&lt;1E-9,2*ROUND((U12)/2,0),ROUND((U12),0)),U12))</f>
+        <v/>
+      </c>
+      <c r="AQ12" s="42" t="n"/>
+      <c r="AR12" s="34" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AS12" s="43" t="n"/>
+      <c r="AT12" s="43" t="n"/>
+      <c r="AU12" s="44" t="n"/>
+      <c r="AV12" s="45">
+        <f>IF(((T12*pax_cap*load_thin*IF(ABS(MOD(ABS((L12*M12*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_thin)/2,0),ROUND((L12*M12*revleg_thin),0)))-(((battery/range_nm)*D12*IF(ABS(MOD(ABS((L12*M12*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_thin)/2,0),ROUND((L12*M12*revleg_thin),0))*VLOOKUP(B12,country_opex,3,FALSE))+W12+X12+Y12+Z12+AA12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((T12*pax_cap*load_thin*IF(ABS(MOD(ABS((L12*M12*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_thin)/2,0),ROUND((L12*M12*revleg_thin),0)))-(((battery/range_nm)*D12*IF(ABS(MOD(ABS((L12*M12*revleg_thin)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_thin)/2,0),ROUND((L12*M12*revleg_thin),0))*VLOOKUP(B12,country_opex,3,FALSE))+W12+X12+Y12+Z12+AA12)))</f>
+        <v/>
+      </c>
+      <c r="AW12" s="45">
+        <f>IF(((T12*pax_cap*IF(B12="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D12*IF(ABS(MOD(ABS((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B12,country_opex,3,FALSE))+W12+X12+Y12+Z12+AA12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((T12*pax_cap*IF(B12="South Korea",korea_mid_load,load_mid)*IF(ABS(MOD(ABS((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid)),0)))-(((battery/range_nm)*D12*IF(ABS(MOD(ABS((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid))/2,0),ROUND((L12*M12*IF(B12="South Korea",korea_mid_revleg,revleg_mid)),0))*VLOOKUP(B12,country_opex,3,FALSE))+W12+X12+Y12+Z12+AA12)))</f>
+        <v/>
+      </c>
+      <c r="AX12" s="45">
+        <f>IF(((T12*pax_cap*load_full*IF(ABS(MOD(ABS((L12*M12*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_full)/2,0),ROUND((L12*M12*revleg_full),0)))-(((battery/range_nm)*D12*IF(ABS(MOD(ABS((L12*M12*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_full)/2,0),ROUND((L12*M12*revleg_full),0))*VLOOKUP(B12,country_opex,3,FALSE))+W12+X12+Y12+Z12+AA12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((T12*pax_cap*load_full*IF(ABS(MOD(ABS((L12*M12*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_full)/2,0),ROUND((L12*M12*revleg_full),0)))-(((battery/range_nm)*D12*IF(ABS(MOD(ABS((L12*M12*revleg_full)),1)-0.5)&lt;1E-9,2*ROUND((L12*M12*revleg_full)/2,0),ROUND((L12*M12*revleg_full),0))*VLOOKUP(B12,country_opex,3,FALSE))+W12+X12+Y12+Z12+AA12)))</f>
+        <v/>
+      </c>
+      <c r="AY12" s="46" t="n"/>
+      <c r="AZ12" s="46" t="n"/>
+      <c r="BA12" s="34" t="inlineStr">
+        <is>
           <t>rn-c16a1627130f</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="47" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>TOTAL / median</t>
         </is>
       </c>
-      <c r="U10" s="48">
-        <f>SUM(U4:U9)</f>
-        <v/>
-      </c>
-      <c r="AD10" s="48">
-        <f>SUM(AD4:AD9)</f>
-        <v/>
-      </c>
-      <c r="AE10" s="49">
-        <f>IF(U10=0,"",AD10/U10)</f>
-        <v/>
-      </c>
-      <c r="AM10" s="50">
-        <f>SUM(AM4:AM9)</f>
-        <v/>
-      </c>
-      <c r="AN10" s="48">
-        <f>SUM(AN4:AN9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="U13" s="48">
+        <f>SUM(U4:U12)</f>
+        <v/>
+      </c>
+      <c r="AD13" s="48">
+        <f>SUM(AD4:AD12)</f>
+        <v/>
+      </c>
+      <c r="AE13" s="49">
+        <f>IF(U13=0,"",AD13/U13)</f>
+        <v/>
+      </c>
+      <c r="AM13" s="50">
+        <f>SUM(AM4:AM12)</f>
+        <v/>
+      </c>
+      <c r="AN13" s="48">
+        <f>SUM(AN4:AN12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Fleet basis</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>Raw vessels (sum)</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>Fleet (rounded once)</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>Market rev/yr (raw sum)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>Indrive Brazil</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>per_corridor_floor</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D14" s="51">
-        <f>SUMIFS(AM4:AM9,A4:A9,"Indrive Brazil",AQ4:AQ9,"=",AR4:AR9,"Grounded")</f>
-        <v/>
-      </c>
-      <c r="E14" s="52">
-        <f>SUMIFS(AN4:AN9,A4:A9,"Indrive Brazil",AQ4:AQ9,"=",AR4:AR9,"Grounded")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="D17" s="51">
+        <f>SUMIFS(AM4:AM12,A4:A12,"Indrive Brazil",AQ4:AQ12,"=",AR4:AR12,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="E17" s="52">
+        <f>SUMIFS(AN4:AN12,A4:A12,"Indrive Brazil",AQ4:AQ12,"=",AR4:AR12,"Grounded")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>Indrive Egypt</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>two luxury-belt captive routes on labeled destination-pool demand at ~90% floor capture; three held</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D15" s="51">
-        <f>SUMIFS(AM4:AM9,A4:A9,"Indrive Egypt",AQ4:AQ9,"=",AR4:AR9,"Grounded")</f>
-        <v/>
-      </c>
-      <c r="E15" s="52">
-        <f>SUMIFS(AN4:AN9,A4:A9,"Indrive Egypt",AQ4:AQ9,"=",AR4:AR9,"Grounded")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="47" t="inlineStr">
+      <c r="D18" s="51">
+        <f>SUMIFS(AM4:AM12,A4:A12,"Indrive Egypt",AQ4:AQ12,"=",AR4:AR12,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="E18" s="52">
+        <f>SUMIFS(AN4:AN12,A4:A12,"Indrive Egypt",AQ4:AQ12,"=",AR4:AR12,"Grounded")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="47" t="inlineStr">
         <is>
           <t>GROUNDED FLOOR (PUBLISHED)</t>
         </is>
       </c>
-      <c r="D16" s="50">
-        <f>SUM(D14:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="48">
-        <f>SUM(E14:E15)</f>
+      <c r="D19" s="50">
+        <f>SUM(D17:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="48">
+        <f>SUM(E17:E18)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A15:L15"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A12:L12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4192,12 +4792,12 @@
         </is>
       </c>
       <c r="C11" s="53">
-        <f>som_floor_rev/(ROUND(SUMPRODUCT(--('Corridor economics'!$AR$4:$AR$9="Grounded"),'Corridor economics'!$AH$4:$AH$9,'Corridor economics'!$E$4:$E$9),0))</f>
+        <f>som_floor_rev/(ROUND(SUMPRODUCT(--('Corridor economics'!$AR$4:$AR$12="Grounded"),'Corridor economics'!$AH$4:$AH$12,'Corridor economics'!$E$4:$E$12),0))</f>
         <v/>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>New-entrant ~12% share of today's pool (= the published floor).</t>
+          <t>New-entrant ~11% share of today's pool (= the published floor).</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4858,7 @@
         </is>
       </c>
       <c r="C16" s="52">
-        <f>ROUND(SUMPRODUCT(--('Corridor economics'!$AR$4:$AR$9="Grounded"),'Corridor economics'!$AH$4:$AH$9,'Corridor economics'!$E$4:$E$9),0)</f>
+        <f>ROUND(SUMPRODUCT(--('Corridor economics'!$AR$4:$AR$12="Grounded"),'Corridor economics'!$AH$4:$AH$12,'Corridor economics'!$E$4:$E$12),0)</f>
         <v/>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -4270,7 +4870,7 @@
     <row r="18">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>SOM full network (~12% capture, today, +greenfield)</t>
+          <t>SOM full network (~11% capture, today, +greenfield)</t>
         </is>
       </c>
       <c r="B18" s="52">
@@ -4287,7 +4887,7 @@
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>Floor posture (~12% captive capture, today's demand) extended across the whole mapped network.</t>
+          <t>Floor posture (~11% captive capture, today's demand) extended across the whole mapped network.</t>
         </is>
       </c>
     </row>

--- a/finance/_refresh_indrive.xlsx
+++ b/finance/_refresh_indrive.xlsx
@@ -3123,11 +3123,11 @@
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>Beira Mar Terminal (continent) → Miramar Terminal (Florianopolis island)</t>
+          <t>Barreiros Terminal (Sao Jose / continent) → Miramar Terminal (Florianopolis island)</t>
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>20</v>
@@ -3238,7 +3238,7 @@
         <v/>
       </c>
       <c r="AH6" s="33" t="n">
-        <v>6100556</v>
+        <v>3890964</v>
       </c>
       <c r="AI6" s="34" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="BA6" s="34" t="inlineStr">
         <is>
-          <t>rn-floripa-r4-PROV</t>
+          <t>rn-36dcca92d821</t>
         </is>
       </c>
     </row>
@@ -3319,11 +3319,11 @@
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>Barreiros Terminal (Sao Jose / continent) → Miramar Terminal (Florianopolis island)</t>
+          <t>Beira Mar Terminal (continent) → Miramar Terminal (Florianopolis island)</t>
         </is>
       </c>
       <c r="D7" s="33" t="n">
-        <v>4.99</v>
+        <v>5.15</v>
       </c>
       <c r="E7" s="27" t="n">
         <v>20</v>
@@ -3434,7 +3434,7 @@
         <v/>
       </c>
       <c r="AH7" s="33" t="n">
-        <v>3890964</v>
+        <v>6100556</v>
       </c>
       <c r="AI7" s="34" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="BA7" s="34" t="inlineStr">
         <is>
-          <t>rn-floripa-r3-PROV</t>
+          <t>rn-7d157e1300da</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="BA10" s="34" t="inlineStr">
         <is>
-          <t>rn-angra-abraao-PROV</t>
+          <t>rn-7ec802385553</t>
         </is>
       </c>
     </row>
